--- a/Lab 2/Generate Files/BOM/Lab 2.xlsx
+++ b/Lab 2/Generate Files/BOM/Lab 2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Session 4\Devlo-session-4\Lab 2\Generate Files\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{695652D1-D360-49AA-9BB9-627071D17AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4ED5A6E4-51D1-4FCF-AB35-FA725FBFFC2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3024" yWindow="2256" windowWidth="17280" windowHeight="8880" xr2:uid="{A9713DD4-99D6-4245-BA95-3978A150E929}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8CE50DC9-4449-4299-9265-237EC828647A}"/>
   </bookViews>
   <sheets>
     <sheet name="Lab 2" sheetId="1" r:id="rId1"/>
@@ -659,23 +659,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF2D27CD-AFBA-4980-B810-78770D2F57CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CFACC92-BBAD-4D88-9782-FDB4892C6DF3}">
   <dimension ref="A1:M11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="31.21875" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" customWidth="1"/>
-    <col min="6" max="6" width="32.33203125" customWidth="1"/>
-    <col min="7" max="7" width="34.33203125" customWidth="1"/>
-    <col min="8" max="9" width="16.33203125" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" customWidth="1"/>
-    <col min="11" max="11" width="28.77734375" customWidth="1"/>
-    <col min="12" max="13" width="16.33203125" customWidth="1"/>
+    <col min="1" max="2" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="32.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="6" max="6" width="33.28515625" customWidth="1"/>
+    <col min="7" max="7" width="35.42578125" customWidth="1"/>
+    <col min="8" max="9" width="16.7109375" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="29.5703125" customWidth="1"/>
+    <col min="12" max="13" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -716,7 +716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
@@ -749,7 +749,7 @@
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -784,7 +784,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="2" t="s">
@@ -817,7 +817,7 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2" t="s">
@@ -850,7 +850,7 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -891,7 +891,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
@@ -916,7 +916,7 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>51</v>
       </c>
@@ -955,7 +955,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="2" t="s">
@@ -988,7 +988,7 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="2" t="s">
@@ -1021,7 +1021,7 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>41</v>
       </c>
